--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1211,34 +1211,34 @@
         <v>2.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
         <v>1.81</v>
@@ -1247,19 +1247,19 @@
         <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,55 +1370,55 @@
         <v>2.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1529,40 +1529,40 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
         <v>1.81</v>
@@ -1571,13 +1571,13 @@
         <v>1.86</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="O8" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.94</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.44</v>
+        <v>4.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>4.94</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>4.1</v>
+        <v>5.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="R8" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.02</v>
+        <v>2.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46209.79166666666</v>
+        <v>46209.77083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="R9" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.4</v>
+        <v>4.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="P10" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2101,6 +2101,324 @@
       </c>
       <c r="AU10" s="3" t="n">
         <v>46209.79166666666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>46209.79166666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Técnico Universitario</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46209.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>4.94</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.94</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.44</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="R10" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>4.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="P11" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -734,28 +734,28 @@
         <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
         <v>1.24</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.94</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.44</v>
+        <v>4.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>4.94</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="V6" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>4.94</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.94</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>2.13</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.44</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.02</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1838,58 +1838,58 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
         <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
         <v>4.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
         <v>1.9</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="P11" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S2" t="n">
         <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
         <v>2.75</v>
@@ -758,22 +758,22 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
         <v>1.1</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -893,49 +893,49 @@
         <v>3.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S3" t="n">
         <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="U3" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
         <v>1.73</v>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,43 +1202,43 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
         <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S5" t="n">
         <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA5" t="n">
         <v>1.53</v>
@@ -1247,19 +1247,19 @@
         <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AD5" t="n">
         <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
         <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,37 +1361,37 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.94</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.23</v>
@@ -1400,25 +1400,25 @@
         <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
         <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
         <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1523,16 +1523,16 @@
         <v>2.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S7" t="n">
         <v>1.17</v>
@@ -1544,7 +1544,7 @@
         <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="W7" t="n">
         <v>1.22</v>
@@ -1553,31 +1553,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.6</v>
+        <v>6.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AF7" t="n">
         <v>1.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1682,77 +1682,77 @@
         <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="Q9" t="n">
         <v>2.59</v>
@@ -1853,7 +1853,7 @@
         <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
         <v>2.65</v>
@@ -1865,19 +1865,19 @@
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
         <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
         <v>1.67</v>
@@ -1886,7 +1886,7 @@
         <v>4.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
         <v>3.15</v>
       </c>
-      <c r="P10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2165,16 +2165,16 @@
         <v>3.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
         <v>3.2</v>
@@ -2186,7 +2186,7 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.37</v>
@@ -2201,7 +2201,7 @@
         <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="AD11" t="n">
         <v>1.21</v>
@@ -2213,7 +2213,7 @@
         <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,25 +2318,25 @@
         <v>1.67</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
         <v>4.33</v>
       </c>
       <c r="Q12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
@@ -2348,31 +2348,31 @@
         <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
         <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
@@ -773,7 +773,7 @@
         <v>3.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
         <v>1.1</v>
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
         <v>2.4</v>
       </c>
       <c r="R3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
         <v>2.79</v>
@@ -917,19 +917,19 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD3" t="n">
         <v>1.27</v>
@@ -938,10 +938,10 @@
         <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.26</v>
       </c>
       <c r="O5" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.85</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.26</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="O7" t="n">
         <v>3.84</v>
@@ -1559,13 +1559,13 @@
         <v>6.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB7" t="n">
         <v>2.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD7" t="n">
         <v>1.85</v>
@@ -1700,10 +1700,10 @@
         <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
         <v>1.09</v>
@@ -1718,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
         <v>2.05</v>
@@ -1733,10 +1733,10 @@
         <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.02</v>
+        <v>4.31</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,28 +1997,28 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
         <v>2.07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U10" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
@@ -2033,7 +2033,7 @@
         <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="AA10" t="n">
         <v>2.1</v>
@@ -2042,19 +2042,19 @@
         <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
         <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="O11" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.65</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.6</v>
       </c>
       <c r="U11" t="n">
         <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.31</v>
+        <v>4.02</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2321,13 +2321,13 @@
         <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S12" t="n">
         <v>1.42</v>
@@ -2351,25 +2351,25 @@
         <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.88</v>
+        <v>3.32</v>
       </c>
       <c r="AA12" t="n">
         <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
         <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
         <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG12" t="n">
         <v>1.76</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.26</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>3.26</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
         <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.04</v>
       </c>
       <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AF11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>3.26</v>
       </c>
       <c r="O5" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.26</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -728,49 +728,49 @@
         <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,34 +884,34 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T3" t="n">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
@@ -929,19 +929,19 @@
         <v>1.78</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
         <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="U5" t="n">
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
         <v>1.09</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
         <v>2.58</v>
@@ -1391,7 +1391,7 @@
         <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.13</v>
@@ -1406,7 +1406,7 @@
         <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
         <v>1.61</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
         <v>3.3</v>
@@ -1535,13 +1535,13 @@
         <v>2.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T7" t="n">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
         <v>1.79</v>
@@ -1559,25 +1559,25 @@
         <v>6.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB7" t="n">
         <v>2.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
         <v>1.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF7" t="n">
         <v>1.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
         <v>1.29</v>
@@ -1682,61 +1682,61 @@
         <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
         <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
         <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK8" t="n">
         <v>2.4</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.45</v>
       </c>
       <c r="U9" t="n">
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.31</v>
+        <v>4.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.02</v>
+        <v>4.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
         <v>2.85</v>
@@ -2174,7 +2174,7 @@
         <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
         <v>3.04</v>
@@ -2192,28 +2192,28 @@
         <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="AA11" t="n">
         <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
         <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.55</v>
+        <v>4.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
         <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
@@ -2348,31 +2348,31 @@
         <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.04</v>
       </c>
       <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AF9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="R11" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
         <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1541,13 +1541,13 @@
         <v>3.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
         <v>1.79</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
         <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.04</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.65</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
         <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.35</v>
+        <v>4.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.04</v>
       </c>
       <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.09</v>
+        <v>3.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.44</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.42</v>
+        <v>3.09</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1679,58 +1679,58 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="R8" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
         <v>1.75</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>3.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
         <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
         <v>1.04</v>
       </c>
       <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.53</v>
@@ -2345,7 +2345,7 @@
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
         <v>1.33</v>
@@ -2354,10 +2354,10 @@
         <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
         <v>3.75</v>
@@ -2372,7 +2372,7 @@
         <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -728,28 +728,28 @@
         <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
       </c>
       <c r="S2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -758,10 +758,10 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.93</v>
@@ -770,19 +770,19 @@
         <v>1.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -884,34 +884,34 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>3.87</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
@@ -923,25 +923,25 @@
         <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
         <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.25</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.28</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.09</v>
+        <v>2.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.09</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="V6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.44</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P7" t="n">
         <v>1.98</v>
@@ -1541,13 +1541,13 @@
         <v>3.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
         <v>1.79</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1562,7 +1562,7 @@
         <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AC7" t="n">
         <v>1.85</v>
@@ -1682,10 +1682,10 @@
         <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
         <v>2.03</v>
@@ -1703,7 +1703,7 @@
         <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
@@ -1715,10 +1715,10 @@
         <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>5.02</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
         <v>2.13</v>
@@ -1727,7 +1727,7 @@
         <v>2.76</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
         <v>1.16</v>
@@ -1736,7 +1736,7 @@
         <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>3.81</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="U10" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
         <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
         <v>1.91</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
         <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
         <v>2.38</v>
@@ -2330,7 +2330,7 @@
         <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
         <v>2.53</v>
@@ -2348,10 +2348,10 @@
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="AA12" t="n">
         <v>2.2</v>
@@ -2360,10 +2360,10 @@
         <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
         <v>1.06</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
         <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC11" t="n">
         <v>3.7</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
         <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
         <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.75</v>
       </c>
-      <c r="U10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.65</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2418,6 +2418,165 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
+        <v>46209.875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
         <v>46209.875</v>
       </c>
     </row>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
         <v>2.05</v>
       </c>
       <c r="S9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.4</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AG9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" t="n">
         <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.04</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>3.34</v>
+        <v>3.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -728,13 +728,13 @@
         <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
         <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
@@ -749,19 +749,19 @@
         <v>2.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.93</v>
@@ -773,16 +773,16 @@
         <v>3.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -890,58 +890,58 @@
         <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>3.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB3" t="n">
         <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
         <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
         <v>2.18</v>
@@ -1226,13 +1226,13 @@
         <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
         <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
         <v>1.23</v>
@@ -1241,22 +1241,22 @@
         <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
         <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
         <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
         <v>2.1</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1364,10 +1364,10 @@
         <v>2.46</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
         <v>2.8</v>
@@ -1376,28 +1376,28 @@
         <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
         <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
         <v>1.53</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
         <v>1.98</v>
@@ -1538,16 +1538,16 @@
         <v>1.19</v>
       </c>
       <c r="T7" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1559,19 +1559,19 @@
         <v>6.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
         <v>1.33</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
         <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
         <v>3.2</v>
@@ -2024,13 +2024,13 @@
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
         <v>2.88</v>
@@ -2039,16 +2039,16 @@
         <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
         <v>1.91</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
         <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>3.34</v>
+        <v>3.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.04</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1211,7 +1211,7 @@
         <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
         <v>2.18</v>
@@ -1250,13 +1250,13 @@
         <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
         <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
         <v>2.1</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
         <v>3.5</v>
@@ -1397,7 +1397,7 @@
         <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="AA6" t="n">
         <v>1.53</v>
@@ -1418,7 +1418,7 @@
         <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
         <v>1.5</v>
@@ -1675,23 +1675,23 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="S8" t="n">
         <v>1.29</v>
@@ -1700,13 +1700,13 @@
         <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
@@ -1715,28 +1715,28 @@
         <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.02</v>
+        <v>4.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
         <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.68</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.4</v>
+        <v>3.68</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.04</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>3.3</v>
@@ -1538,7 +1538,7 @@
         <v>1.19</v>
       </c>
       <c r="T7" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="U7" t="n">
         <v>1.91</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
         <v>1.28</v>
@@ -2021,10 +2021,10 @@
         <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
@@ -2039,16 +2039,16 @@
         <v>2.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
         <v>2.05</v>
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="R11" t="n">
         <v>2.13</v>
@@ -2186,13 +2186,13 @@
         <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
         <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
         <v>2.2</v>
@@ -2201,7 +2201,7 @@
         <v>1.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
         <v>1.2</v>
@@ -2213,7 +2213,7 @@
         <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="R8" t="n">
         <v>2.47</v>
@@ -1712,16 +1712,16 @@
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
         <v>4.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
         <v>2.63</v>
@@ -1733,10 +1733,10 @@
         <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
         <v>2.38</v>
@@ -1841,52 +1841,52 @@
         <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
         <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="R9" t="n">
         <v>1.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
         <v>2.86</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
         <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
@@ -1895,7 +1895,7 @@
         <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
         <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.5</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
         <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U12" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="V12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.25</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.44</v>
+        <v>4.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>3.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.85</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
@@ -1688,10 +1688,10 @@
         <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="R8" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="S8" t="n">
         <v>1.29</v>
@@ -1703,7 +1703,7 @@
         <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
         <v>1.12</v>
@@ -1715,28 +1715,28 @@
         <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1841,61 +1841,61 @@
         <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2000,61 +2000,61 @@
         <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="R10" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
         <v>2.5</v>
@@ -2186,19 +2186,19 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AA11" t="n">
         <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
         <v>4.35</v>
@@ -2207,7 +2207,7 @@
         <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
         <v>2.05</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="n">
         <v>2.5</v>
@@ -2333,13 +2333,13 @@
         <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
         <v>1.06</v>
@@ -2354,13 +2354,13 @@
         <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD12" t="n">
         <v>1.23</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q2" t="n">
         <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S2" t="n">
         <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -758,10 +758,10 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.93</v>
@@ -770,19 +770,19 @@
         <v>1.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>3.87</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
         <v>2.2</v>
@@ -899,7 +899,7 @@
         <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.97</v>
@@ -911,22 +911,22 @@
         <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AC3" t="n">
         <v>2.83</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
         <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
         <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
         <v>1.22</v>
@@ -1235,10 +1235,10 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.53</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S6" t="n">
         <v>1.35</v>
@@ -1394,7 +1394,7 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
         <v>3.44</v>
@@ -1406,7 +1406,7 @@
         <v>1.96</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AD6" t="n">
         <v>1.33</v>
@@ -1434,7 +1434,7 @@
         <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>3.32</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P7" t="n">
         <v>1.87</v>
@@ -1535,16 +1535,16 @@
         <v>2.6</v>
       </c>
       <c r="S7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="U7" t="n">
         <v>1.91</v>
       </c>
       <c r="V7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W7" t="n">
         <v>1.19</v>
@@ -1559,19 +1559,19 @@
         <v>6.26</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
         <v>1.33</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.79</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,13 +1688,13 @@
         <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
         <v>3.25</v>
@@ -1718,13 +1718,13 @@
         <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
         <v>1.47</v>
@@ -1752,7 +1752,7 @@
         <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
         <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>4.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,19 +2006,19 @@
         <v>3.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.88</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="V10" t="n">
         <v>1.31</v>
@@ -2027,13 +2027,13 @@
         <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AA10" t="n">
         <v>2.08</v>
@@ -2051,10 +2051,10 @@
         <v>1.05</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
         <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
         <v>3.8</v>
@@ -2327,10 +2327,10 @@
         <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
         <v>2.62</v>
@@ -2348,10 +2348,10 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="AA12" t="n">
         <v>2.01</v>
@@ -2360,13 +2360,13 @@
         <v>1.74</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
         <v>1.9</v>
@@ -2483,13 +2483,13 @@
         <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R13" t="n">
         <v>2.06</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
         <v>2.36</v>
@@ -2504,13 +2504,13 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
         <v>2.31</v>
@@ -2522,16 +2522,16 @@
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
         <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2000,61 +2000,61 @@
         <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="S10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2159,61 +2159,61 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.05</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.24</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.94</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" t="n">
         <v>3.2</v>
       </c>
-      <c r="P9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
         <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.36</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA10" t="n">
         <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>4.36</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE10" t="n">
         <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -731,7 +731,7 @@
         <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q2" t="n">
         <v>2.88</v>
@@ -740,10 +740,10 @@
         <v>1.98</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
         <v>2.79</v>
@@ -752,16 +752,16 @@
         <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.93</v>
@@ -779,10 +779,10 @@
         <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
         <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
         <v>2.56</v>
@@ -914,31 +914,31 @@
         <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
         <v>1.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
         <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
         <v>1.95</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.24</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.94</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>3.24</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.61</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1685,34 +1685,34 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>2.57</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V8" t="n">
         <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
         <v>4.4</v>
@@ -1730,7 +1730,7 @@
         <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
         <v>1.67</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
         <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>4.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
         <v>3.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
         <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.36</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
         <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
         <v>3.8</v>
@@ -2333,10 +2333,10 @@
         <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
@@ -2345,19 +2345,19 @@
         <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.66</v>
+        <v>2.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>3.34</v>
@@ -2366,7 +2366,7 @@
         <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF12" t="n">
         <v>1.9</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -731,7 +731,7 @@
         <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>2.88</v>
@@ -887,13 +887,13 @@
         <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
         <v>4.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R3" t="n">
         <v>2.3</v>
@@ -902,13 +902,13 @@
         <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
         <v>1.1</v>
@@ -917,28 +917,28 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
         <v>1.95</v>
@@ -957,7 +957,7 @@
         <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>3.24</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.44</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
         <v>3.65</v>
@@ -1556,16 +1556,16 @@
         <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.26</v>
+        <v>6.36</v>
       </c>
       <c r="AA7" t="n">
         <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD7" t="n">
         <v>1.85</v>
@@ -1679,34 +1679,34 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="S8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
         <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
@@ -1718,19 +1718,19 @@
         <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
         <v>1.67</v>
@@ -1752,7 +1752,7 @@
         <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
         <v>2.5</v>
@@ -1865,10 +1865,10 @@
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y9" t="n">
         <v>1.4</v>
@@ -1877,13 +1877,13 @@
         <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB9" t="n">
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.36</v>
+        <v>4.44</v>
       </c>
       <c r="AD9" t="n">
         <v>1.16</v>
@@ -1892,10 +1892,10 @@
         <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2000,61 +2000,61 @@
         <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="S10" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.33</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
         <v>3.8</v>
@@ -2330,28 +2330,28 @@
         <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
         <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA12" t="n">
         <v>2.05</v>
@@ -2360,13 +2360,13 @@
         <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
         <v>1.9</v>
@@ -2477,52 +2477,52 @@
         <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
         <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
         <v>1.01</v>
@@ -2531,7 +2531,7 @@
         <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="O9" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
         <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
         <v>3.4</v>
@@ -1868,13 +1868,13 @@
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
         <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
         <v>2.21</v>
@@ -1883,10 +1883,10 @@
         <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
@@ -1911,7 +1911,7 @@
         <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.81</v>
       </c>
       <c r="Q11" t="n">
         <v>2.59</v>
@@ -2192,13 +2192,13 @@
         <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AA11" t="n">
         <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
         <v>3.84</v>
@@ -2207,7 +2207,7 @@
         <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
         <v>1.94</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1523,7 +1523,7 @@
         <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
         <v>1.87</v>
@@ -1541,13 +1541,13 @@
         <v>3.94</v>
       </c>
       <c r="U7" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V7" t="n">
         <v>1.79</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1562,7 +1562,7 @@
         <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AC7" t="n">
         <v>1.94</v>
@@ -1571,7 +1571,7 @@
         <v>1.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF7" t="n">
         <v>1.33</v>
@@ -1685,58 +1685,58 @@
         <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
         <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U9" t="n">
         <v>3.2</v>
       </c>
-      <c r="P9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.54</v>
+        <v>3.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
         <v>2.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
         <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
         <v>1.75</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.81</v>
+        <v>3.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.84</v>
+        <v>4.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="U12" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="O13" t="n">
-        <v>3.24</v>
+        <v>3.44</v>
       </c>
       <c r="P13" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="T13" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.44</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>3.24</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.61</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1694,13 +1694,13 @@
         <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="V8" t="n">
         <v>1.5</v>
@@ -1709,13 +1709,13 @@
         <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
         <v>1.67</v>
@@ -1724,16 +1724,16 @@
         <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
         <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
         <v>1.93</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.84</v>
+        <v>4.59</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
         <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T10" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="U10" t="n">
         <v>3.04</v>
@@ -2036,13 +2036,13 @@
         <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AB10" t="n">
         <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD10" t="n">
         <v>1.19</v>
@@ -2051,7 +2051,7 @@
         <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
         <v>1.85</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U11" t="n">
         <v>3.2</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.54</v>
+        <v>3.84</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -740,7 +740,7 @@
         <v>1.98</v>
       </c>
       <c r="S2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T2" t="n">
         <v>2.67</v>
@@ -749,19 +749,19 @@
         <v>2.79</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.93</v>
@@ -770,7 +770,7 @@
         <v>1.76</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
         <v>1.25</v>
@@ -779,10 +779,10 @@
         <v>1.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T10" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="U10" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.1</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.59</v>
-      </c>
       <c r="R11" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="S11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.05</v>
@@ -2189,47 +2189,47 @@
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,31 +2348,31 @@
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -884,43 +884,43 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P3" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S3" t="n">
         <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U3" t="n">
         <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
         <v>1.8</v>
@@ -929,19 +929,19 @@
         <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
         <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="Q5" t="n">
         <v>2.8</v>
@@ -1226,7 +1226,7 @@
         <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1244,7 +1244,7 @@
         <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AC5" t="n">
         <v>2.25</v>
@@ -1253,13 +1253,13 @@
         <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
         <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1364,16 +1364,16 @@
         <v>3.24</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
         <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
         <v>1.36</v>
@@ -1397,22 +1397,22 @@
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AA6" t="n">
         <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
         <v>1.67</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>3.36</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
         <v>1.87</v>
@@ -1532,13 +1532,13 @@
         <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S7" t="n">
         <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="U7" t="n">
         <v>1.94</v>
@@ -1556,13 +1556,13 @@
         <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.36</v>
+        <v>6.52</v>
       </c>
       <c r="AA7" t="n">
         <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
         <v>1.94</v>
@@ -1571,13 +1571,13 @@
         <v>1.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AF7" t="n">
         <v>1.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.79</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,46 +1688,46 @@
         <v>4.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="U8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
         <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
         <v>1.14</v>
@@ -1736,7 +1736,7 @@
         <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T9" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
         <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.59</v>
+        <v>3.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.1</v>
       </c>
-      <c r="P10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.59</v>
-      </c>
       <c r="R10" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T10" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
@@ -2030,47 +2030,47 @@
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="P11" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.59</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
         <v>3.4</v>
@@ -2501,7 +2501,7 @@
         <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
@@ -2513,7 +2513,7 @@
         <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
         <v>1.72</v>
@@ -2528,10 +2528,10 @@
         <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.59</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.84</v>
+        <v>4.59</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T10" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="U10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
@@ -2030,31 +2030,31 @@
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
         <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="S11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.59</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T9" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.59</v>
+        <v>3.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="O10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P10" t="n">
         <v>3.15</v>
       </c>
-      <c r="P10" t="n">
-        <v>3.7</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T10" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
@@ -2030,31 +2030,31 @@
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
         <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="P11" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.59</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,40 +1202,40 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
         <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
         <v>5</v>
@@ -1250,16 +1250,16 @@
         <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF5" t="n">
         <v>1.44</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
         <v>1.36</v>
@@ -1382,10 +1382,10 @@
         <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1397,28 +1397,28 @@
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
         <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -721,68 +721,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
         <v>3.1</v>
       </c>
       <c r="P2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.67</v>
-      </c>
       <c r="U2" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC2" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46209.53125</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -873,118 +873,118 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '80']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46209.54166666666</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>3.32</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.65</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.61</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,34 +1520,34 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.36</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
         <v>2.62</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T7" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1556,28 +1556,28 @@
         <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.52</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
         <v>1.28</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.45</v>
+        <v>5.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.47</v>
       </c>
       <c r="V8" t="n">
         <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.93</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,31 +1841,31 @@
         <v>1.98</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
         <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
@@ -1874,22 +1874,22 @@
         <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
         <v>1.94</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>4.51</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>3.55</v>
+        <v>3.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>2.91</v>
+        <v>3.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1170,139 +1170,139 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.44</v>
+        <v>5.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '83']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '41', '73', '86']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46209.58333333334</v>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1357,111 +1357,111 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.4</v>
       </c>
-      <c r="AG6" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46209.58333333334</v>
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="S7" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="T7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="W7" t="n">
         <v>1.25</v>
@@ -1556,44 +1556,44 @@
         <v>1.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.28</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
-        <v>5.81</v>
+        <v>6.25</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
@@ -1694,16 +1694,16 @@
         <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.08</v>
+        <v>3.33</v>
       </c>
       <c r="U8" t="n">
         <v>2.47</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W8" t="n">
         <v>1.14</v>
@@ -1712,31 +1712,31 @@
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.93</v>
+        <v>5.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V9" t="n">
         <v>1.32</v>
@@ -1871,31 +1871,31 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
         <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
         <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.51</v>
+        <v>4.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>3.24</v>
+        <v>4.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U11" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.04</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
         <v>3.25</v>
@@ -2330,10 +2330,10 @@
         <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
         <v>2.91</v>
@@ -2342,7 +2342,7 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
@@ -2360,19 +2360,19 @@
         <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
         <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-07-06.xlsx
+++ b/jogos_2026-07-06.xlsx
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1509,14 +1509,14 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,16 +1599,16 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,139 +1806,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.24</v>
+        <v>4.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['28', '54', '79']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.32</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46209.79166666666</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,28 +1997,28 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.87</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V10" t="n">
         <v>1.32</v>
@@ -2030,31 +2030,31 @@
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
         <v>1.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,139 +2124,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>4.39</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
         <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '90+2']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR11" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46209.79166666666</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2318,61 +2318,61 @@
         <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S12" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>3.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2477,61 +2477,61 @@
         <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>3.58</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
